--- a/shows-ive-seen/data/concert_ticket_dataset.xlsx
+++ b/shows-ive-seen/data/concert_ticket_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2878f7d885d1c7bd/Documents/Website/Shows Ive Seen/shows-ive-seen/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{ED4AB0C9-CB1F-4FE0-8DA8-0F9542F64B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F57D38DA-EA1B-48E0-ABC0-39D31E5DB227}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{ED4AB0C9-CB1F-4FE0-8DA8-0F9542F64B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{679687B7-C5A7-4D1A-8844-269670843039}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="719">
   <si>
     <t>image_filename</t>
   </si>
@@ -109,9 +109,6 @@
     <t>Gris Gris at Emo's in Austin in 2006</t>
   </si>
   <si>
-    <t>Image filename suggests supplementary material or a detail view. Venue inferred from filename is uncertain.</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>Adele at Madison Square Garden during the Adele Live 2016, tour for the 25 album.</t>
   </si>
   <si>
-    <t>Image filename suggests supplementary material or a detail view.</t>
-  </si>
-  <si>
     <t>adele-radio-city-music-hall-2015.jpg</t>
   </si>
   <si>
@@ -190,9 +184,6 @@
     <t>Aimee Mann at Hogg Memorial Auditorium in Austin in 2005</t>
   </si>
   <si>
-    <t>Image filename suggests supplementary material or a detail view. Exact date not cleanly legible from OCR.</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -724,9 +715,6 @@
     <t>Courtney Barnett at Lucinda's in 2025</t>
   </si>
   <si>
-    <t>Image filename suggests supplementary material or a detail view. This file appears to document related ephemera rather than a standard front-facing ticket.</t>
-  </si>
-  <si>
     <t>courtney-barnett-music-hall-of-williamsburg-2014.jpg</t>
   </si>
   <si>
@@ -2090,6 +2078,105 @@
   </si>
   <si>
     <t>Yaz</t>
+  </si>
+  <si>
+    <t>is_festival</t>
+  </si>
+  <si>
+    <t>festival_name</t>
+  </si>
+  <si>
+    <t>festival_id</t>
+  </si>
+  <si>
+    <t>festival_dates</t>
+  </si>
+  <si>
+    <t>festival_day_label</t>
+  </si>
+  <si>
+    <t>artists_seen</t>
+  </si>
+  <si>
+    <t>artists_noted</t>
+  </si>
+  <si>
+    <t>festival_summary</t>
+  </si>
+  <si>
+    <t>youtube_videos</t>
+  </si>
+  <si>
+    <t>all-points-west-festival-liberty-state-park-2008.jpg</t>
+  </si>
+  <si>
+    <t>All Points West</t>
+  </si>
+  <si>
+    <t>Liberty State Park</t>
+  </si>
+  <si>
+    <t>festival | vip | sunday</t>
+  </si>
+  <si>
+    <t>all-points-west-liberty-state-park-2008</t>
+  </si>
+  <si>
+    <t>all-points-west-2008</t>
+  </si>
+  <si>
+    <t>2008-08-08 to 2008-08-10</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Cat Power | Rodrigo y Gabriela</t>
+  </si>
+  <si>
+    <t>2008 All Points West Festival Day 3</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>All Points West at Liberty State Park on August 10, 2008. My first time at Liberty State Park, a trek that felt far until the Manhattan skyline came into full view from the grounds. I was there with my coworker Jenna P., most excited for Cat Power’s Jukebox era set that I had been playing all summer. Rain shaped the day, but the experience held, with Rodrigo y Gabriela a strong follow after seeing them earlier in Austin, even if I was still kicking myself for missing Radiohead the days before.</t>
+  </si>
+  <si>
+    <t>Day-specific Sunday ticket. GA VIP Radio credential. Festival dates: 2008-08-08 to 2008-08-10. Rain impacted scheduling on Sunday. Artists seen confirmed by user: Cat Power | Rodrigo y Gabriela.</t>
+  </si>
+  <si>
+    <t>austin-city-limits-festival-2002_brochure_front.jpg</t>
+  </si>
+  <si>
+    <t>Austin City Limits Music Festival</t>
+  </si>
+  <si>
+    <t>Zilker Park</t>
+  </si>
+  <si>
+    <t>austin-city-limits-music-festival-zilker-park-2002</t>
+  </si>
+  <si>
+    <t>ACL Festival 2002 Day 1</t>
+  </si>
+  <si>
+    <t>festival | saturday | inaugural</t>
+  </si>
+  <si>
+    <t>Austin City Limits Music Festival at Zilker Park on September 28, 2002. The first-ever ACL Festival, spent in the heat of Zilker Park with my best friend Kristen P., figuring out the experience in real time as the now-iconic event took shape. I was most focused on catching Wilco, even with the pull of Patty Griffin playing at the same time, and at one point got paid $20 by a stranger to use my cell phone, something that felt normal then and strange now. A formative day that’s taken on more meaning as ACL has become such a defining part of Austin’s culture.</t>
+  </si>
+  <si>
+    <t>Attended Saturday only (user confirmed). Inaugural ACL Festival. High heat conditions noted. Wilco prioritized based on user memory; other artists not explicitly confirmed.</t>
+  </si>
+  <si>
+    <t>acl-2002</t>
+  </si>
+  <si>
+    <t>2002-09-28 to 2002-09-29</t>
+  </si>
+  <si>
+    <t>Saturday</t>
   </si>
 </sst>
 </file>
@@ -2145,11 +2232,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2456,15 +2544,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T139"/>
+  <dimension ref="A1:AC141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="61.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
     <col min="17" max="17" width="137.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.6640625" customWidth="1"/>
+    <col min="21" max="21" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2493,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -2525,8 +2626,35 @@
       <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U1" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2560,22 +2688,22 @@
       <c r="Q2" t="s">
         <v>28</v>
       </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
       <c r="S2">
         <v>0.95</v>
       </c>
       <c r="T2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -2593,42 +2721,42 @@
         <v>2005</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3">
         <v>13</v>
       </c>
       <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
         <v>34</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" t="s">
-        <v>29</v>
       </c>
       <c r="S3">
         <v>0.95</v>
       </c>
       <c r="T3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
@@ -2637,45 +2765,45 @@
         <v>2016</v>
       </c>
       <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
         <v>41</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>42</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>43</v>
       </c>
-      <c r="M4" t="s">
+      <c r="Q4" t="s">
         <v>44</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" t="s">
-        <v>46</v>
       </c>
       <c r="S4">
         <v>0.98</v>
       </c>
       <c r="T4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
@@ -2684,36 +2812,36 @@
         <v>2015</v>
       </c>
       <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" t="s">
         <v>49</v>
-      </c>
-      <c r="L5" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>51</v>
-      </c>
-      <c r="R5" t="s">
-        <v>46</v>
       </c>
       <c r="S5">
         <v>0.95</v>
       </c>
       <c r="T5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
         <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -2728,30 +2856,30 @@
         <v>2005</v>
       </c>
       <c r="Q6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="S6">
         <v>0.8</v>
       </c>
       <c r="T6" t="s">
+        <v>54</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
         <v>58</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -2763,33 +2891,33 @@
         <v>2000</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="s">
-        <v>64</v>
-      </c>
-      <c r="R7" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="S7">
         <v>0.95</v>
       </c>
       <c r="T7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -2804,33 +2932,33 @@
         <v>2007</v>
       </c>
       <c r="Q8" t="s">
-        <v>68</v>
-      </c>
-      <c r="R8" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="S8">
         <v>0.8</v>
       </c>
       <c r="T8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -2839,39 +2967,39 @@
         <v>2011</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="s">
-        <v>74</v>
-      </c>
-      <c r="R9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="S9">
         <v>0.85</v>
       </c>
       <c r="T9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -2880,127 +3008,127 @@
         <v>2010</v>
       </c>
       <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q10" t="s">
         <v>78</v>
-      </c>
-      <c r="I10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P10" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>81</v>
-      </c>
-      <c r="R10" t="s">
-        <v>46</v>
       </c>
       <c r="S10">
         <v>0.95</v>
       </c>
       <c r="T10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
         <v>82</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>83</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" t="s">
-        <v>87</v>
       </c>
       <c r="G11">
         <v>2017</v>
       </c>
       <c r="H11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" t="s">
         <v>88</v>
       </c>
-      <c r="I11" t="s">
+      <c r="P11" t="s">
         <v>89</v>
       </c>
-      <c r="L11" t="s">
+      <c r="Q11" t="s">
         <v>90</v>
-      </c>
-      <c r="M11" t="s">
-        <v>91</v>
-      </c>
-      <c r="P11" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>93</v>
-      </c>
-      <c r="R11" t="s">
-        <v>46</v>
       </c>
       <c r="S11">
         <v>0.98</v>
       </c>
       <c r="T11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" t="s">
         <v>94</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" t="s">
-        <v>97</v>
       </c>
       <c r="G12">
         <v>2010</v>
       </c>
       <c r="L12" t="s">
+        <v>95</v>
+      </c>
+      <c r="M12" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12" t="s">
         <v>98</v>
-      </c>
-      <c r="M12" t="s">
-        <v>99</v>
-      </c>
-      <c r="P12" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>101</v>
-      </c>
-      <c r="R12" t="s">
-        <v>56</v>
       </c>
       <c r="S12">
         <v>0.9</v>
       </c>
       <c r="T12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -3015,42 +3143,42 @@
         <v>2005</v>
       </c>
       <c r="H13" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13" t="s">
         <v>104</v>
-      </c>
-      <c r="L13" t="s">
-        <v>105</v>
-      </c>
-      <c r="M13" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" t="s">
-        <v>46</v>
       </c>
       <c r="S13">
         <v>0.95</v>
       </c>
       <c r="T13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -3059,45 +3187,45 @@
         <v>2010</v>
       </c>
       <c r="H14" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" t="s">
+        <v>110</v>
+      </c>
+      <c r="M14" t="s">
         <v>111</v>
       </c>
-      <c r="I14" t="s">
+      <c r="Q14" t="s">
         <v>112</v>
-      </c>
-      <c r="L14" t="s">
-        <v>113</v>
-      </c>
-      <c r="M14" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R14" t="s">
-        <v>46</v>
       </c>
       <c r="S14">
         <v>0.98</v>
       </c>
       <c r="T14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
         <v>24</v>
@@ -3106,39 +3234,39 @@
         <v>2012</v>
       </c>
       <c r="H15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q15" t="s">
-        <v>121</v>
-      </c>
-      <c r="R15" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="S15">
         <v>0.9</v>
       </c>
       <c r="T15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
@@ -3147,42 +3275,42 @@
         <v>2008</v>
       </c>
       <c r="I16" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" t="s">
+        <v>123</v>
+      </c>
+      <c r="M16" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q16" t="s">
         <v>125</v>
-      </c>
-      <c r="L16" t="s">
-        <v>126</v>
-      </c>
-      <c r="M16" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>128</v>
-      </c>
-      <c r="R16" t="s">
-        <v>56</v>
       </c>
       <c r="S16">
         <v>0.9</v>
       </c>
       <c r="T16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" t="s">
         <v>129</v>
       </c>
-      <c r="B17" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" t="s">
-        <v>131</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
-      </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
         <v>24</v>
@@ -3191,36 +3319,36 @@
         <v>2018</v>
       </c>
       <c r="H17" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" t="s">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q17" t="s">
         <v>133</v>
-      </c>
-      <c r="I17" t="s">
-        <v>134</v>
-      </c>
-      <c r="L17" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>136</v>
-      </c>
-      <c r="R17" t="s">
-        <v>46</v>
       </c>
       <c r="S17">
         <v>0.98</v>
       </c>
       <c r="T17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
@@ -3235,39 +3363,39 @@
         <v>2003</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q18" t="s">
-        <v>142</v>
-      </c>
-      <c r="R18" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="S18">
         <v>0.9</v>
       </c>
       <c r="T18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -3276,39 +3404,39 @@
         <v>2013</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="L19" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q19" t="s">
-        <v>148</v>
-      </c>
-      <c r="R19" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="S19">
         <v>0.9</v>
       </c>
       <c r="T19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
         <v>24</v>
@@ -3317,27 +3445,27 @@
         <v>2019</v>
       </c>
       <c r="H20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q20" t="s">
-        <v>153</v>
-      </c>
-      <c r="R20" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="S20">
         <v>0.9</v>
       </c>
       <c r="T20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -3355,39 +3483,39 @@
         <v>2004</v>
       </c>
       <c r="H21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" t="s">
+        <v>155</v>
+      </c>
+      <c r="P21" t="s">
         <v>156</v>
       </c>
-      <c r="I21" t="s">
+      <c r="Q21" t="s">
         <v>157</v>
-      </c>
-      <c r="K21" t="s">
-        <v>158</v>
-      </c>
-      <c r="P21" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>160</v>
-      </c>
-      <c r="R21" t="s">
-        <v>46</v>
       </c>
       <c r="S21">
         <v>0.95</v>
       </c>
       <c r="T21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -3402,39 +3530,39 @@
         <v>1997</v>
       </c>
       <c r="H22" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q22" t="s">
-        <v>166</v>
-      </c>
-      <c r="R22" t="s">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="S22">
         <v>0.95</v>
       </c>
       <c r="T22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" t="s">
         <v>38</v>
       </c>
-      <c r="D23" t="s">
-        <v>39</v>
-      </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
         <v>24</v>
@@ -3443,45 +3571,45 @@
         <v>2015</v>
       </c>
       <c r="H23" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" t="s">
+        <v>166</v>
+      </c>
+      <c r="L23" t="s">
+        <v>167</v>
+      </c>
+      <c r="M23" t="s">
         <v>168</v>
       </c>
-      <c r="I23" t="s">
+      <c r="Q23" t="s">
         <v>169</v>
-      </c>
-      <c r="L23" t="s">
-        <v>170</v>
-      </c>
-      <c r="M23" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>172</v>
-      </c>
-      <c r="R23" t="s">
-        <v>46</v>
       </c>
       <c r="S23">
         <v>0.98</v>
       </c>
       <c r="T23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
         <v>24</v>
@@ -3490,33 +3618,33 @@
         <v>2008</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q24" t="s">
-        <v>177</v>
-      </c>
-      <c r="R24" t="s">
-        <v>46</v>
+        <v>174</v>
       </c>
       <c r="S24">
         <v>0.95</v>
       </c>
       <c r="T24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -3531,33 +3659,33 @@
         <v>2005</v>
       </c>
       <c r="Q25" t="s">
-        <v>180</v>
-      </c>
-      <c r="R25" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="S25">
         <v>0.8</v>
       </c>
       <c r="T25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
         <v>38</v>
       </c>
-      <c r="D26" t="s">
-        <v>39</v>
-      </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
@@ -3566,42 +3694,42 @@
         <v>2009</v>
       </c>
       <c r="I26" t="s">
+        <v>180</v>
+      </c>
+      <c r="L26" t="s">
+        <v>181</v>
+      </c>
+      <c r="M26" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q26" t="s">
         <v>183</v>
-      </c>
-      <c r="L26" t="s">
-        <v>184</v>
-      </c>
-      <c r="M26" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>186</v>
-      </c>
-      <c r="R26" t="s">
-        <v>56</v>
       </c>
       <c r="S26">
         <v>0.9</v>
       </c>
       <c r="T26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s">
         <v>24</v>
@@ -3610,39 +3738,39 @@
         <v>2014</v>
       </c>
       <c r="H27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I27" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q27" t="s">
-        <v>191</v>
-      </c>
-      <c r="R27" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="S27">
         <v>0.95</v>
       </c>
       <c r="T27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
         <v>24</v>
@@ -3651,42 +3779,42 @@
         <v>2008</v>
       </c>
       <c r="H28" t="s">
+        <v>191</v>
+      </c>
+      <c r="L28" t="s">
+        <v>192</v>
+      </c>
+      <c r="M28" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q28" t="s">
         <v>194</v>
-      </c>
-      <c r="L28" t="s">
-        <v>195</v>
-      </c>
-      <c r="M28" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>197</v>
-      </c>
-      <c r="R28" t="s">
-        <v>46</v>
       </c>
       <c r="S28">
         <v>0.98</v>
       </c>
       <c r="T28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
         <v>24</v>
@@ -3695,36 +3823,36 @@
         <v>2009</v>
       </c>
       <c r="I29" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q29" t="s">
-        <v>202</v>
-      </c>
-      <c r="R29" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="S29">
         <v>0.85</v>
       </c>
       <c r="T29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" t="s">
         <v>203</v>
       </c>
-      <c r="B30" t="s">
+      <c r="E30" t="s">
         <v>204</v>
-      </c>
-      <c r="C30" t="s">
-        <v>205</v>
-      </c>
-      <c r="D30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E30" t="s">
-        <v>207</v>
       </c>
       <c r="F30" t="s">
         <v>24</v>
@@ -3733,30 +3861,30 @@
         <v>2022</v>
       </c>
       <c r="H30" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q30" t="s">
-        <v>210</v>
-      </c>
-      <c r="R30" t="s">
-        <v>46</v>
+        <v>207</v>
       </c>
       <c r="S30">
         <v>0.95</v>
       </c>
       <c r="T30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B31" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -3774,42 +3902,42 @@
         <v>2007</v>
       </c>
       <c r="H31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
       </c>
       <c r="P31" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q31" t="s">
-        <v>214</v>
-      </c>
-      <c r="R31" t="s">
-        <v>46</v>
+        <v>211</v>
       </c>
       <c r="S31">
         <v>0.95</v>
       </c>
       <c r="T31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C32" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s">
         <v>24</v>
@@ -3818,36 +3946,36 @@
         <v>2007</v>
       </c>
       <c r="H32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q32" t="s">
-        <v>219</v>
-      </c>
-      <c r="R32" t="s">
-        <v>46</v>
+        <v>216</v>
       </c>
       <c r="S32">
         <v>0.9</v>
       </c>
       <c r="T32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
         <v>24</v>
@@ -3856,36 +3984,36 @@
         <v>2017</v>
       </c>
       <c r="I33" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q33" t="s">
-        <v>223</v>
-      </c>
-      <c r="R33" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="S33">
         <v>0.85</v>
       </c>
       <c r="T33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -3894,42 +4022,42 @@
         <v>2015</v>
       </c>
       <c r="I34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q34" t="s">
-        <v>228</v>
-      </c>
-      <c r="R34" t="s">
-        <v>56</v>
+        <v>225</v>
       </c>
       <c r="S34">
         <v>0.9</v>
       </c>
       <c r="T34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F35" t="s">
         <v>24</v>
@@ -3938,39 +4066,39 @@
         <v>2025</v>
       </c>
       <c r="H35" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q35" t="s">
-        <v>233</v>
-      </c>
-      <c r="R35" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="S35">
         <v>0.7</v>
       </c>
       <c r="T35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C36" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
         <v>24</v>
@@ -3979,36 +4107,36 @@
         <v>2014</v>
       </c>
       <c r="I36" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q36" t="s">
-        <v>237</v>
-      </c>
-      <c r="R36" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="S36">
         <v>0.85</v>
       </c>
       <c r="T36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
         <v>24</v>
@@ -4017,42 +4145,42 @@
         <v>2015</v>
       </c>
       <c r="I37" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L37" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q37" t="s">
-        <v>240</v>
-      </c>
-      <c r="R37" t="s">
-        <v>56</v>
+        <v>236</v>
       </c>
       <c r="S37">
         <v>0.9</v>
       </c>
       <c r="T37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C38" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F38" t="s">
         <v>24</v>
@@ -4061,39 +4189,39 @@
         <v>2011</v>
       </c>
       <c r="H38" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I38" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Q38" t="s">
-        <v>245</v>
-      </c>
-      <c r="R38" t="s">
-        <v>46</v>
+        <v>241</v>
       </c>
       <c r="S38">
         <v>0.95</v>
       </c>
       <c r="T38" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B39" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
         <v>38</v>
       </c>
-      <c r="D39" t="s">
-        <v>39</v>
-      </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
         <v>24</v>
@@ -4102,39 +4230,39 @@
         <v>2015</v>
       </c>
       <c r="H39" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L39" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="Q39" t="s">
-        <v>250</v>
-      </c>
-      <c r="R39" t="s">
-        <v>46</v>
+        <v>246</v>
       </c>
       <c r="S39">
         <v>0.95</v>
       </c>
       <c r="T39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F40" t="s">
         <v>24</v>
@@ -4143,45 +4271,45 @@
         <v>2019</v>
       </c>
       <c r="H40" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I40" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L40" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M40" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q40" t="s">
-        <v>256</v>
-      </c>
-      <c r="R40" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="S40">
         <v>0.98</v>
       </c>
       <c r="T40" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
         <v>24</v>
@@ -4190,36 +4318,36 @@
         <v>2010</v>
       </c>
       <c r="I41" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q41" t="s">
-        <v>259</v>
-      </c>
-      <c r="R41" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="S41">
         <v>0.85</v>
       </c>
       <c r="T41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C42" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s">
         <v>24</v>
@@ -4228,27 +4356,27 @@
         <v>2015</v>
       </c>
       <c r="Q42" t="s">
-        <v>263</v>
-      </c>
-      <c r="R42" t="s">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="S42">
         <v>0.8</v>
       </c>
       <c r="T42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B43" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C43" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
         <v>22</v>
@@ -4263,33 +4391,33 @@
         <v>1999</v>
       </c>
       <c r="Q43" t="s">
-        <v>267</v>
-      </c>
-      <c r="R43" t="s">
-        <v>56</v>
+        <v>263</v>
       </c>
       <c r="S43">
         <v>0.8</v>
       </c>
       <c r="T43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B44" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C44" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F44" t="s">
         <v>24</v>
@@ -4298,42 +4426,42 @@
         <v>2018</v>
       </c>
       <c r="I44" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="L44" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="M44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="Q44" t="s">
-        <v>273</v>
-      </c>
-      <c r="R44" t="s">
-        <v>56</v>
+        <v>269</v>
       </c>
       <c r="S44">
         <v>0.9</v>
       </c>
       <c r="T44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
         <v>24</v>
@@ -4342,48 +4470,48 @@
         <v>2011</v>
       </c>
       <c r="H45" t="s">
+        <v>273</v>
+      </c>
+      <c r="I45" t="s">
+        <v>274</v>
+      </c>
+      <c r="L45" t="s">
+        <v>275</v>
+      </c>
+      <c r="M45" t="s">
+        <v>276</v>
+      </c>
+      <c r="P45" t="s">
         <v>277</v>
       </c>
-      <c r="I45" t="s">
+      <c r="Q45" t="s">
         <v>278</v>
-      </c>
-      <c r="L45" t="s">
-        <v>279</v>
-      </c>
-      <c r="M45" t="s">
-        <v>280</v>
-      </c>
-      <c r="P45" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>282</v>
-      </c>
-      <c r="R45" t="s">
-        <v>46</v>
       </c>
       <c r="S45">
         <v>0.98</v>
       </c>
       <c r="T45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B46" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" t="s">
         <v>38</v>
       </c>
-      <c r="D46" t="s">
-        <v>39</v>
-      </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
         <v>24</v>
@@ -4392,39 +4520,39 @@
         <v>2015</v>
       </c>
       <c r="H46" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L46" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="Q46" t="s">
-        <v>287</v>
-      </c>
-      <c r="R46" t="s">
-        <v>46</v>
+        <v>283</v>
       </c>
       <c r="S46">
         <v>0.95</v>
       </c>
       <c r="T46" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B47" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F47" t="s">
         <v>24</v>
@@ -4433,39 +4561,39 @@
         <v>2010</v>
       </c>
       <c r="H47" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I47" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q47" t="s">
-        <v>291</v>
-      </c>
-      <c r="R47" t="s">
-        <v>46</v>
+        <v>287</v>
       </c>
       <c r="S47">
         <v>0.95</v>
       </c>
       <c r="T47" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C48" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D48" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E48" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
         <v>24</v>
@@ -4474,39 +4602,39 @@
         <v>2014</v>
       </c>
       <c r="I48" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L48" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="Q48" t="s">
-        <v>298</v>
-      </c>
-      <c r="R48" t="s">
-        <v>56</v>
+        <v>294</v>
       </c>
       <c r="S48">
         <v>0.9</v>
       </c>
       <c r="T48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B49" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C49" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F49" t="s">
         <v>24</v>
@@ -4515,30 +4643,30 @@
         <v>2017</v>
       </c>
       <c r="I49" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="Q49" t="s">
-        <v>302</v>
-      </c>
-      <c r="R49" t="s">
-        <v>56</v>
+        <v>298</v>
       </c>
       <c r="S49">
         <v>0.85</v>
       </c>
       <c r="T49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
         <v>22</v>
@@ -4553,33 +4681,33 @@
         <v>2006</v>
       </c>
       <c r="H50" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="Q50" t="s">
-        <v>306</v>
-      </c>
-      <c r="R50" t="s">
-        <v>46</v>
+        <v>302</v>
       </c>
       <c r="S50">
         <v>0.9</v>
       </c>
       <c r="T50" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
         <v>23</v>
@@ -4591,36 +4719,36 @@
         <v>2000</v>
       </c>
       <c r="I51" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Q51" t="s">
-        <v>310</v>
-      </c>
-      <c r="R51" t="s">
-        <v>56</v>
+        <v>306</v>
       </c>
       <c r="S51">
         <v>0.85</v>
       </c>
       <c r="T51" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B52" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C52" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F52" t="s">
         <v>24</v>
@@ -4629,36 +4757,36 @@
         <v>2015</v>
       </c>
       <c r="I52" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Q52" t="s">
-        <v>313</v>
-      </c>
-      <c r="R52" t="s">
-        <v>56</v>
+        <v>309</v>
       </c>
       <c r="S52">
         <v>0.85</v>
       </c>
       <c r="T52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B53" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C53" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F53" t="s">
         <v>24</v>
@@ -4667,42 +4795,42 @@
         <v>2016</v>
       </c>
       <c r="I53" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L53" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M53" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="Q53" t="s">
-        <v>320</v>
-      </c>
-      <c r="R53" t="s">
-        <v>56</v>
+        <v>316</v>
       </c>
       <c r="S53">
         <v>0.9</v>
       </c>
       <c r="T53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s">
         <v>24</v>
@@ -4711,42 +4839,42 @@
         <v>2013</v>
       </c>
       <c r="I54" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L54" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M54" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Q54" t="s">
-        <v>326</v>
-      </c>
-      <c r="R54" t="s">
-        <v>56</v>
+        <v>322</v>
       </c>
       <c r="S54">
         <v>0.9</v>
       </c>
       <c r="T54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B55" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" t="s">
         <v>38</v>
       </c>
-      <c r="D55" t="s">
-        <v>39</v>
-      </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F55" t="s">
         <v>24</v>
@@ -4755,42 +4883,42 @@
         <v>2018</v>
       </c>
       <c r="I55" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="L55" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M55" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="Q55" t="s">
-        <v>331</v>
-      </c>
-      <c r="R55" t="s">
-        <v>56</v>
+        <v>327</v>
       </c>
       <c r="S55">
         <v>0.9</v>
       </c>
       <c r="T55" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B56" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C56" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" t="s">
         <v>38</v>
       </c>
-      <c r="D56" t="s">
-        <v>39</v>
-      </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F56" t="s">
         <v>24</v>
@@ -4799,45 +4927,45 @@
         <v>2008</v>
       </c>
       <c r="H56" t="s">
+        <v>330</v>
+      </c>
+      <c r="I56" t="s">
+        <v>331</v>
+      </c>
+      <c r="L56" t="s">
+        <v>332</v>
+      </c>
+      <c r="M56" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q56" t="s">
         <v>334</v>
-      </c>
-      <c r="I56" t="s">
-        <v>335</v>
-      </c>
-      <c r="L56" t="s">
-        <v>336</v>
-      </c>
-      <c r="M56" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>338</v>
-      </c>
-      <c r="R56" t="s">
-        <v>46</v>
       </c>
       <c r="S56">
         <v>0.98</v>
       </c>
       <c r="T56" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C57" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" t="s">
         <v>38</v>
       </c>
-      <c r="D57" t="s">
-        <v>39</v>
-      </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F57" t="s">
         <v>24</v>
@@ -4846,39 +4974,39 @@
         <v>2010</v>
       </c>
       <c r="H57" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I57" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="Q57" t="s">
-        <v>343</v>
-      </c>
-      <c r="R57" t="s">
-        <v>46</v>
+        <v>339</v>
       </c>
       <c r="S57">
         <v>0.95</v>
       </c>
       <c r="T57" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B58" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F58" t="s">
         <v>24</v>
@@ -4887,30 +5015,30 @@
         <v>2016</v>
       </c>
       <c r="L58" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M58" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="Q58" t="s">
-        <v>348</v>
-      </c>
-      <c r="R58" t="s">
-        <v>56</v>
+        <v>344</v>
       </c>
       <c r="S58">
         <v>0.85</v>
       </c>
       <c r="T58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C59" t="s">
         <v>21</v>
@@ -4928,36 +5056,36 @@
         <v>2008</v>
       </c>
       <c r="H59" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I59" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="P59" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q59" t="s">
-        <v>353</v>
-      </c>
-      <c r="R59" t="s">
-        <v>46</v>
+        <v>349</v>
       </c>
       <c r="S59">
         <v>0.95</v>
       </c>
       <c r="T59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B60" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C60" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -4972,30 +5100,30 @@
         <v>2008</v>
       </c>
       <c r="H60" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="Q60" t="s">
-        <v>358</v>
-      </c>
-      <c r="R60" t="s">
-        <v>46</v>
+        <v>354</v>
       </c>
       <c r="S60">
         <v>0.9</v>
       </c>
       <c r="T60" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B61" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C61" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D61" t="s">
         <v>22</v>
@@ -5010,27 +5138,27 @@
         <v>2004</v>
       </c>
       <c r="Q61" t="s">
-        <v>362</v>
-      </c>
-      <c r="R61" t="s">
-        <v>56</v>
+        <v>358</v>
       </c>
       <c r="S61">
         <v>0.8</v>
       </c>
       <c r="T61" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B62" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
         <v>22</v>
@@ -5045,80 +5173,80 @@
         <v>2002</v>
       </c>
       <c r="H62" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="Q62" t="s">
-        <v>365</v>
-      </c>
-      <c r="R62" t="s">
-        <v>46</v>
+        <v>361</v>
       </c>
       <c r="S62">
         <v>0.9</v>
       </c>
       <c r="T62" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>362</v>
+      </c>
+      <c r="B63" t="s">
+        <v>363</v>
+      </c>
+      <c r="C63" t="s">
+        <v>364</v>
+      </c>
+      <c r="D63" t="s">
+        <v>365</v>
+      </c>
+      <c r="F63" t="s">
         <v>366</v>
-      </c>
-      <c r="B63" t="s">
-        <v>367</v>
-      </c>
-      <c r="C63" t="s">
-        <v>368</v>
-      </c>
-      <c r="D63" t="s">
-        <v>369</v>
-      </c>
-      <c r="F63" t="s">
-        <v>370</v>
       </c>
       <c r="G63">
         <v>2012</v>
       </c>
       <c r="H63" t="s">
+        <v>367</v>
+      </c>
+      <c r="L63" t="s">
+        <v>368</v>
+      </c>
+      <c r="M63" t="s">
+        <v>369</v>
+      </c>
+      <c r="P63" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q63" t="s">
         <v>371</v>
-      </c>
-      <c r="L63" t="s">
-        <v>372</v>
-      </c>
-      <c r="M63" t="s">
-        <v>373</v>
-      </c>
-      <c r="P63" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>375</v>
-      </c>
-      <c r="R63" t="s">
-        <v>46</v>
       </c>
       <c r="S63">
         <v>0.95</v>
       </c>
       <c r="T63" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B64" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C64" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" t="s">
         <v>38</v>
       </c>
-      <c r="D64" t="s">
-        <v>39</v>
-      </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F64" t="s">
         <v>24</v>
@@ -5127,39 +5255,39 @@
         <v>2004</v>
       </c>
       <c r="L64" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M64" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="Q64" t="s">
-        <v>380</v>
-      </c>
-      <c r="R64" t="s">
-        <v>56</v>
+        <v>376</v>
       </c>
       <c r="S64">
         <v>0.9</v>
       </c>
       <c r="T64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B65" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" t="s">
         <v>38</v>
       </c>
-      <c r="D65" t="s">
-        <v>39</v>
-      </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F65" t="s">
         <v>24</v>
@@ -5168,39 +5296,39 @@
         <v>2012</v>
       </c>
       <c r="H65" t="s">
+        <v>378</v>
+      </c>
+      <c r="I65" t="s">
+        <v>379</v>
+      </c>
+      <c r="L65" t="s">
+        <v>380</v>
+      </c>
+      <c r="M65" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q65" t="s">
         <v>382</v>
-      </c>
-      <c r="I65" t="s">
-        <v>383</v>
-      </c>
-      <c r="L65" t="s">
-        <v>384</v>
-      </c>
-      <c r="M65" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>386</v>
-      </c>
-      <c r="R65" t="s">
-        <v>46</v>
       </c>
       <c r="S65">
         <v>0.98</v>
       </c>
       <c r="T65" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
         <v>22</v>
@@ -5215,30 +5343,30 @@
         <v>2005</v>
       </c>
       <c r="H66" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="Q66" t="s">
-        <v>390</v>
-      </c>
-      <c r="R66" t="s">
-        <v>46</v>
+        <v>386</v>
       </c>
       <c r="S66">
         <v>0.9</v>
       </c>
       <c r="T66" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
         <v>22</v>
@@ -5253,27 +5381,27 @@
         <v>2003</v>
       </c>
       <c r="Q67" t="s">
-        <v>392</v>
-      </c>
-      <c r="R67" t="s">
-        <v>56</v>
+        <v>388</v>
       </c>
       <c r="S67">
         <v>0.8</v>
       </c>
       <c r="T67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
         <v>22</v>
@@ -5288,33 +5416,33 @@
         <v>2004</v>
       </c>
       <c r="Q68" t="s">
-        <v>394</v>
-      </c>
-      <c r="R68" t="s">
-        <v>56</v>
+        <v>390</v>
       </c>
       <c r="S68">
         <v>0.8</v>
       </c>
       <c r="T68" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C69" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F69" t="s">
         <v>24</v>
@@ -5323,33 +5451,33 @@
         <v>2015</v>
       </c>
       <c r="Q69" t="s">
-        <v>396</v>
-      </c>
-      <c r="R69" t="s">
-        <v>56</v>
+        <v>392</v>
       </c>
       <c r="S69">
         <v>0.8</v>
       </c>
       <c r="T69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B70" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F70" t="s">
         <v>24</v>
@@ -5358,39 +5486,39 @@
         <v>2010</v>
       </c>
       <c r="H70" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="P70" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q70" t="s">
-        <v>400</v>
-      </c>
-      <c r="R70" t="s">
-        <v>46</v>
+        <v>396</v>
       </c>
       <c r="S70">
         <v>0.9</v>
       </c>
       <c r="T70" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B71" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F71" t="s">
         <v>24</v>
@@ -5399,39 +5527,39 @@
         <v>2010</v>
       </c>
       <c r="H71" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I71" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="Q71" t="s">
-        <v>404</v>
-      </c>
-      <c r="R71" t="s">
-        <v>46</v>
+        <v>400</v>
       </c>
       <c r="S71">
         <v>0.95</v>
       </c>
       <c r="T71" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B72" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F72" t="s">
         <v>24</v>
@@ -5440,36 +5568,36 @@
         <v>2021</v>
       </c>
       <c r="H72" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="L72" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="M72" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Q72" t="s">
-        <v>408</v>
-      </c>
-      <c r="R72" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
       <c r="S72">
         <v>0.95</v>
       </c>
       <c r="T72" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B73" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D73" t="s">
         <v>22</v>
@@ -5484,39 +5612,39 @@
         <v>2006</v>
       </c>
       <c r="H73" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="I73" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="Q73" t="s">
-        <v>412</v>
-      </c>
-      <c r="R73" t="s">
-        <v>46</v>
+        <v>408</v>
       </c>
       <c r="S73">
         <v>0.95</v>
       </c>
       <c r="T73" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B74" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C74" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F74" t="s">
         <v>24</v>
@@ -5525,27 +5653,27 @@
         <v>2008</v>
       </c>
       <c r="Q74" t="s">
-        <v>416</v>
-      </c>
-      <c r="R74" t="s">
-        <v>56</v>
+        <v>412</v>
       </c>
       <c r="S74">
         <v>0.8</v>
       </c>
       <c r="T74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C75" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D75" t="s">
         <v>22</v>
@@ -5560,27 +5688,27 @@
         <v>2004</v>
       </c>
       <c r="H75" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="Q75" t="s">
-        <v>420</v>
-      </c>
-      <c r="R75" t="s">
-        <v>46</v>
+        <v>416</v>
       </c>
       <c r="S75">
         <v>0.9</v>
       </c>
       <c r="T75" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B76" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C76" t="s">
         <v>21</v>
@@ -5598,39 +5726,39 @@
         <v>2004</v>
       </c>
       <c r="I76" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P76" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q76" t="s">
-        <v>423</v>
-      </c>
-      <c r="R76" t="s">
-        <v>56</v>
+        <v>419</v>
       </c>
       <c r="S76">
         <v>0.85</v>
       </c>
       <c r="T76" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B77" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C77" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D77" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F77" t="s">
         <v>24</v>
@@ -5639,36 +5767,36 @@
         <v>2017</v>
       </c>
       <c r="H77" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="Q77" t="s">
-        <v>428</v>
-      </c>
-      <c r="R77" t="s">
-        <v>46</v>
+        <v>424</v>
       </c>
       <c r="S77">
         <v>0.9</v>
       </c>
       <c r="T77" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C78" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D78" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F78" t="s">
         <v>24</v>
@@ -5677,36 +5805,36 @@
         <v>2018</v>
       </c>
       <c r="H78" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="Q78" t="s">
-        <v>431</v>
-      </c>
-      <c r="R78" t="s">
-        <v>46</v>
+        <v>427</v>
       </c>
       <c r="S78">
         <v>0.9</v>
       </c>
       <c r="T78" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B79" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C79" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F79" t="s">
         <v>24</v>
@@ -5715,33 +5843,33 @@
         <v>2009</v>
       </c>
       <c r="H79" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="Q79" t="s">
-        <v>435</v>
-      </c>
-      <c r="R79" t="s">
-        <v>46</v>
+        <v>431</v>
       </c>
       <c r="S79">
         <v>0.9</v>
       </c>
       <c r="T79" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B80" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C80" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D80" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E80" t="s">
         <v>23</v>
@@ -5753,33 +5881,33 @@
         <v>2004</v>
       </c>
       <c r="H80" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L80" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="Q80" t="s">
-        <v>441</v>
-      </c>
-      <c r="R80" t="s">
-        <v>46</v>
+        <v>437</v>
       </c>
       <c r="S80">
         <v>0.95</v>
       </c>
       <c r="T80" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B81" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D81" t="s">
         <v>22</v>
@@ -5794,36 +5922,36 @@
         <v>2004</v>
       </c>
       <c r="L81" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="Q81" t="s">
-        <v>443</v>
-      </c>
-      <c r="R81" t="s">
-        <v>56</v>
+        <v>439</v>
       </c>
       <c r="S81">
         <v>0.85</v>
       </c>
       <c r="T81" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B82" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C82" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F82" t="s">
         <v>24</v>
@@ -5832,39 +5960,39 @@
         <v>2009</v>
       </c>
       <c r="H82" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="I82" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="Q82" t="s">
-        <v>448</v>
-      </c>
-      <c r="R82" t="s">
-        <v>46</v>
+        <v>444</v>
       </c>
       <c r="S82">
         <v>0.95</v>
       </c>
       <c r="T82" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B83" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C83" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D83" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F83" t="s">
         <v>24</v>
@@ -5873,45 +6001,45 @@
         <v>2017</v>
       </c>
       <c r="H83" t="s">
+        <v>447</v>
+      </c>
+      <c r="K83" t="s">
+        <v>448</v>
+      </c>
+      <c r="L83" t="s">
+        <v>449</v>
+      </c>
+      <c r="M83" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q83" t="s">
         <v>451</v>
-      </c>
-      <c r="K83" t="s">
-        <v>452</v>
-      </c>
-      <c r="L83" t="s">
-        <v>453</v>
-      </c>
-      <c r="M83" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>455</v>
-      </c>
-      <c r="R83" t="s">
-        <v>46</v>
       </c>
       <c r="S83">
         <v>0.95</v>
       </c>
       <c r="T83" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C84" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F84" t="s">
         <v>24</v>
@@ -5920,33 +6048,33 @@
         <v>2009</v>
       </c>
       <c r="Q84" t="s">
-        <v>458</v>
-      </c>
-      <c r="R84" t="s">
-        <v>56</v>
+        <v>454</v>
       </c>
       <c r="S84">
         <v>0.8</v>
       </c>
       <c r="T84" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B85" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C85" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D85" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E85" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F85" t="s">
         <v>24</v>
@@ -5955,36 +6083,36 @@
         <v>2018</v>
       </c>
       <c r="I85" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="L85" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M85" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Q85" t="s">
-        <v>464</v>
-      </c>
-      <c r="R85" t="s">
-        <v>56</v>
+        <v>460</v>
       </c>
       <c r="S85">
         <v>0.9</v>
       </c>
       <c r="T85" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -5999,45 +6127,45 @@
         <v>2017</v>
       </c>
       <c r="H86" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="I86" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L86" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M86" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Q86" t="s">
-        <v>467</v>
-      </c>
-      <c r="R86" t="s">
-        <v>46</v>
+        <v>463</v>
       </c>
       <c r="S86">
         <v>0.98</v>
       </c>
       <c r="T86" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B87" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F87" t="s">
         <v>24</v>
@@ -6046,39 +6174,39 @@
         <v>2011</v>
       </c>
       <c r="H87" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I87" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="Q87" t="s">
-        <v>471</v>
-      </c>
-      <c r="R87" t="s">
-        <v>46</v>
+        <v>467</v>
       </c>
       <c r="S87">
         <v>0.95</v>
       </c>
       <c r="T87" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B88" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C88" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F88" t="s">
         <v>24</v>
@@ -6087,42 +6215,42 @@
         <v>2016</v>
       </c>
       <c r="I88" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="L88" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M88" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="Q88" t="s">
-        <v>474</v>
-      </c>
-      <c r="R88" t="s">
-        <v>56</v>
+        <v>470</v>
       </c>
       <c r="S88">
         <v>0.9</v>
       </c>
       <c r="T88" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B89" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C89" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F89" t="s">
         <v>24</v>
@@ -6131,36 +6259,36 @@
         <v>2012</v>
       </c>
       <c r="I89" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q89" t="s">
-        <v>477</v>
-      </c>
-      <c r="R89" t="s">
-        <v>56</v>
+        <v>473</v>
       </c>
       <c r="S89">
         <v>0.85</v>
       </c>
       <c r="T89" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B90" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C90" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F90" t="s">
         <v>24</v>
@@ -6169,45 +6297,45 @@
         <v>2013</v>
       </c>
       <c r="H90" t="s">
+        <v>477</v>
+      </c>
+      <c r="I90" t="s">
+        <v>478</v>
+      </c>
+      <c r="L90" t="s">
+        <v>479</v>
+      </c>
+      <c r="M90" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q90" t="s">
         <v>481</v>
-      </c>
-      <c r="I90" t="s">
-        <v>482</v>
-      </c>
-      <c r="L90" t="s">
-        <v>483</v>
-      </c>
-      <c r="M90" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>485</v>
-      </c>
-      <c r="R90" t="s">
-        <v>46</v>
       </c>
       <c r="S90">
         <v>0.98</v>
       </c>
       <c r="T90" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B91" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C91" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F91" t="s">
         <v>24</v>
@@ -6216,36 +6344,36 @@
         <v>2014</v>
       </c>
       <c r="I91" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="Q91" t="s">
-        <v>488</v>
-      </c>
-      <c r="R91" t="s">
-        <v>56</v>
+        <v>484</v>
       </c>
       <c r="S91">
         <v>0.85</v>
       </c>
       <c r="T91" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B92" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F92" t="s">
         <v>24</v>
@@ -6254,39 +6382,39 @@
         <v>2008</v>
       </c>
       <c r="H92" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="I92" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Q92" t="s">
-        <v>492</v>
-      </c>
-      <c r="R92" t="s">
-        <v>46</v>
+        <v>488</v>
       </c>
       <c r="S92">
         <v>0.95</v>
       </c>
       <c r="T92" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C93" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93" t="s">
         <v>38</v>
       </c>
-      <c r="D93" t="s">
-        <v>39</v>
-      </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F93" t="s">
         <v>24</v>
@@ -6295,36 +6423,36 @@
         <v>2013</v>
       </c>
       <c r="I93" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="L93" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="Q93" t="s">
-        <v>498</v>
-      </c>
-      <c r="R93" t="s">
-        <v>56</v>
+        <v>494</v>
       </c>
       <c r="S93">
         <v>0.9</v>
       </c>
       <c r="T93" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B94" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C94" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D94" t="s">
         <v>22</v>
@@ -6339,62 +6467,62 @@
         <v>2007</v>
       </c>
       <c r="Q94" t="s">
-        <v>501</v>
-      </c>
-      <c r="R94" t="s">
-        <v>56</v>
+        <v>497</v>
       </c>
       <c r="S94">
         <v>0.8</v>
       </c>
       <c r="T94" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B95" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C95" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D95" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G95">
         <v>2010</v>
       </c>
       <c r="P95" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q95" t="s">
-        <v>505</v>
-      </c>
-      <c r="R95" t="s">
-        <v>56</v>
+        <v>501</v>
       </c>
       <c r="S95">
         <v>0.8</v>
       </c>
       <c r="T95" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B96" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D96" t="s">
         <v>22</v>
@@ -6409,30 +6537,30 @@
         <v>2006</v>
       </c>
       <c r="H96" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="I96" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="Q96" t="s">
-        <v>508</v>
-      </c>
-      <c r="R96" t="s">
-        <v>46</v>
+        <v>504</v>
       </c>
       <c r="S96">
         <v>0.95</v>
       </c>
       <c r="T96" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C97" t="s">
         <v>21</v>
@@ -6450,39 +6578,39 @@
         <v>2006</v>
       </c>
       <c r="H97" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="P97" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q97" t="s">
-        <v>512</v>
-      </c>
-      <c r="R97" t="s">
-        <v>46</v>
+        <v>508</v>
       </c>
       <c r="S97">
         <v>0.9</v>
       </c>
       <c r="T97" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B98" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D98" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E98" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F98" t="s">
         <v>24</v>
@@ -6491,39 +6619,39 @@
         <v>2024</v>
       </c>
       <c r="L98" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="P98" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="Q98" t="s">
-        <v>517</v>
-      </c>
-      <c r="R98" t="s">
-        <v>56</v>
+        <v>513</v>
       </c>
       <c r="S98">
         <v>0.85</v>
       </c>
       <c r="T98" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B99" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C99" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D99" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F99" t="s">
         <v>24</v>
@@ -6535,39 +6663,39 @@
         <v>33</v>
       </c>
       <c r="L99" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="M99" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="Q99" t="s">
-        <v>522</v>
-      </c>
-      <c r="R99" t="s">
-        <v>56</v>
+        <v>518</v>
       </c>
       <c r="S99">
         <v>0.9</v>
       </c>
       <c r="T99" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B100" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C100" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D100" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F100" t="s">
         <v>24</v>
@@ -6576,30 +6704,30 @@
         <v>2015</v>
       </c>
       <c r="I100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q100" t="s">
-        <v>524</v>
-      </c>
-      <c r="R100" t="s">
-        <v>56</v>
+        <v>520</v>
       </c>
       <c r="S100">
         <v>0.85</v>
       </c>
       <c r="T100" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B101" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C101" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D101" t="s">
         <v>22</v>
@@ -6614,36 +6742,36 @@
         <v>2006</v>
       </c>
       <c r="H101" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="Q101" t="s">
-        <v>528</v>
-      </c>
-      <c r="R101" t="s">
-        <v>46</v>
+        <v>524</v>
       </c>
       <c r="S101">
         <v>0.9</v>
       </c>
       <c r="T101" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B102" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C102" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D102" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F102" t="s">
         <v>24</v>
@@ -6652,45 +6780,45 @@
         <v>2014</v>
       </c>
       <c r="H102" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I102" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="L102" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="M102" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="Q102" t="s">
-        <v>534</v>
-      </c>
-      <c r="R102" t="s">
-        <v>46</v>
+        <v>530</v>
       </c>
       <c r="S102">
         <v>0.98</v>
       </c>
       <c r="T102" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B103" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C103" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F103" t="s">
         <v>24</v>
@@ -6699,39 +6827,39 @@
         <v>2013</v>
       </c>
       <c r="H103" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I103" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="Q103" t="s">
-        <v>540</v>
-      </c>
-      <c r="R103" t="s">
-        <v>46</v>
+        <v>536</v>
       </c>
       <c r="S103">
         <v>0.95</v>
       </c>
       <c r="T103" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F104" t="s">
         <v>24</v>
@@ -6740,36 +6868,36 @@
         <v>2010</v>
       </c>
       <c r="I104" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q104" t="s">
-        <v>543</v>
-      </c>
-      <c r="R104" t="s">
-        <v>56</v>
+        <v>539</v>
       </c>
       <c r="S104">
         <v>0.85</v>
       </c>
       <c r="T104" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B105" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -6778,39 +6906,39 @@
         <v>2008</v>
       </c>
       <c r="H105" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="I105">
         <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>547</v>
-      </c>
-      <c r="R105" t="s">
-        <v>46</v>
+        <v>543</v>
       </c>
       <c r="S105">
         <v>0.95</v>
       </c>
       <c r="T105" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B106" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D106" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F106" t="s">
         <v>24</v>
@@ -6819,39 +6947,39 @@
         <v>2008</v>
       </c>
       <c r="H106" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I106" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="Q106" t="s">
-        <v>552</v>
-      </c>
-      <c r="R106" t="s">
-        <v>46</v>
+        <v>548</v>
       </c>
       <c r="S106">
         <v>0.95</v>
       </c>
       <c r="T106" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B107" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C107" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F107" t="s">
         <v>24</v>
@@ -6860,39 +6988,39 @@
         <v>2013</v>
       </c>
       <c r="I107" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L107" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="Q107" t="s">
-        <v>555</v>
-      </c>
-      <c r="R107" t="s">
-        <v>56</v>
+        <v>551</v>
       </c>
       <c r="S107">
         <v>0.9</v>
       </c>
       <c r="T107" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B108" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F108" t="s">
         <v>24</v>
@@ -6901,45 +7029,45 @@
         <v>2013</v>
       </c>
       <c r="H108" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I108">
         <v>60</v>
       </c>
       <c r="L108" t="s">
+        <v>550</v>
+      </c>
+      <c r="P108" t="s">
         <v>554</v>
       </c>
-      <c r="P108" t="s">
-        <v>558</v>
-      </c>
       <c r="Q108" t="s">
-        <v>555</v>
-      </c>
-      <c r="R108" t="s">
-        <v>46</v>
+        <v>551</v>
       </c>
       <c r="S108">
         <v>0.98</v>
       </c>
       <c r="T108" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B109" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C109" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F109" t="s">
         <v>24</v>
@@ -6948,39 +7076,39 @@
         <v>2013</v>
       </c>
       <c r="H109" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="I109" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="L109" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="P109" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="Q109" t="s">
-        <v>555</v>
-      </c>
-      <c r="R109" t="s">
-        <v>46</v>
+        <v>551</v>
       </c>
       <c r="S109">
         <v>0.98</v>
       </c>
       <c r="T109" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B110" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C110" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D110" t="s">
         <v>22</v>
@@ -6995,39 +7123,39 @@
         <v>2000</v>
       </c>
       <c r="L110" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M110" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="Q110" t="s">
-        <v>568</v>
-      </c>
-      <c r="R110" t="s">
-        <v>56</v>
+        <v>564</v>
       </c>
       <c r="S110">
         <v>0.85</v>
       </c>
       <c r="T110" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B111" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C111" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D111" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F111" t="s">
         <v>24</v>
@@ -7036,30 +7164,30 @@
         <v>2010</v>
       </c>
       <c r="H111" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="I111" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q111" t="s">
-        <v>573</v>
-      </c>
-      <c r="R111" t="s">
-        <v>46</v>
+        <v>569</v>
       </c>
       <c r="S111">
         <v>0.95</v>
       </c>
       <c r="T111" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B112" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C112" t="s">
         <v>21</v>
@@ -7077,33 +7205,33 @@
         <v>2002</v>
       </c>
       <c r="H112" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="P112" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q112" t="s">
-        <v>577</v>
-      </c>
-      <c r="R112" t="s">
-        <v>46</v>
+        <v>573</v>
       </c>
       <c r="S112">
         <v>0.9</v>
       </c>
       <c r="T112" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B113" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C113" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D113" t="s">
         <v>22</v>
@@ -7118,65 +7246,65 @@
         <v>2004</v>
       </c>
       <c r="Q113" t="s">
-        <v>579</v>
-      </c>
-      <c r="R113" t="s">
-        <v>56</v>
+        <v>575</v>
       </c>
       <c r="S113">
         <v>0.8</v>
       </c>
       <c r="T113" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C114" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D114" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F114" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G114">
         <v>2011</v>
       </c>
       <c r="I114" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="P114" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="Q114" t="s">
-        <v>585</v>
-      </c>
-      <c r="R114" t="s">
-        <v>56</v>
+        <v>581</v>
       </c>
       <c r="S114">
         <v>0.85</v>
       </c>
       <c r="T114" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B115" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D115" t="s">
         <v>22</v>
@@ -7191,36 +7319,36 @@
         <v>2006</v>
       </c>
       <c r="H115" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="Q115" t="s">
-        <v>588</v>
-      </c>
-      <c r="R115" t="s">
-        <v>46</v>
+        <v>584</v>
       </c>
       <c r="S115">
         <v>0.9</v>
       </c>
       <c r="T115" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B116" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C116" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F116" t="s">
         <v>24</v>
@@ -7229,39 +7357,39 @@
         <v>2014</v>
       </c>
       <c r="H116" t="s">
+        <v>587</v>
+      </c>
+      <c r="I116" t="s">
+        <v>588</v>
+      </c>
+      <c r="L116" t="s">
+        <v>589</v>
+      </c>
+      <c r="M116" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q116" t="s">
         <v>591</v>
-      </c>
-      <c r="I116" t="s">
-        <v>592</v>
-      </c>
-      <c r="L116" t="s">
-        <v>593</v>
-      </c>
-      <c r="M116" t="s">
-        <v>594</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>595</v>
-      </c>
-      <c r="R116" t="s">
-        <v>46</v>
       </c>
       <c r="S116">
         <v>0.98</v>
       </c>
       <c r="T116" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B117" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D117" t="s">
         <v>22</v>
@@ -7276,30 +7404,30 @@
         <v>2006</v>
       </c>
       <c r="H117" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="Q117" t="s">
-        <v>599</v>
-      </c>
-      <c r="R117" t="s">
-        <v>46</v>
+        <v>595</v>
       </c>
       <c r="S117">
         <v>0.9</v>
       </c>
       <c r="T117" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B118" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D118" t="s">
         <v>22</v>
@@ -7314,33 +7442,33 @@
         <v>2004</v>
       </c>
       <c r="Q118" t="s">
-        <v>602</v>
-      </c>
-      <c r="R118" t="s">
-        <v>56</v>
+        <v>598</v>
       </c>
       <c r="S118">
         <v>0.8</v>
       </c>
       <c r="T118" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B119" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C119" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D119" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F119" t="s">
         <v>24</v>
@@ -7349,39 +7477,39 @@
         <v>2008</v>
       </c>
       <c r="H119" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="I119" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q119" t="s">
-        <v>607</v>
-      </c>
-      <c r="R119" t="s">
-        <v>46</v>
+        <v>603</v>
       </c>
       <c r="S119">
         <v>0.95</v>
       </c>
       <c r="T119" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B120" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F120" t="s">
         <v>24</v>
@@ -7390,33 +7518,33 @@
         <v>2010</v>
       </c>
       <c r="H120" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="I120" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Q120" t="s">
-        <v>610</v>
-      </c>
-      <c r="R120" t="s">
-        <v>46</v>
+        <v>606</v>
       </c>
       <c r="S120">
         <v>0.95</v>
       </c>
       <c r="T120" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B121" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C121" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D121" t="s">
         <v>22</v>
@@ -7431,27 +7559,27 @@
         <v>1997</v>
       </c>
       <c r="Q121" t="s">
-        <v>613</v>
-      </c>
-      <c r="R121" t="s">
-        <v>56</v>
+        <v>609</v>
       </c>
       <c r="S121">
         <v>0.8</v>
       </c>
       <c r="T121" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B122" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D122" t="s">
         <v>22</v>
@@ -7466,39 +7594,39 @@
         <v>2003</v>
       </c>
       <c r="H122" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="I122" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="Q122" t="s">
-        <v>618</v>
-      </c>
-      <c r="R122" t="s">
-        <v>46</v>
+        <v>614</v>
       </c>
       <c r="S122">
         <v>0.95</v>
       </c>
       <c r="T122" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B123" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C123" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D123" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F123" t="s">
         <v>24</v>
@@ -7507,39 +7635,39 @@
         <v>2016</v>
       </c>
       <c r="H123" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="I123" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="Q123" t="s">
-        <v>623</v>
-      </c>
-      <c r="R123" t="s">
-        <v>46</v>
+        <v>619</v>
       </c>
       <c r="S123">
         <v>0.95</v>
       </c>
       <c r="T123" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B124" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C124" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D124" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F124" t="s">
         <v>24</v>
@@ -7548,36 +7676,36 @@
         <v>2013</v>
       </c>
       <c r="I124" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="Q124" t="s">
-        <v>625</v>
-      </c>
-      <c r="R124" t="s">
-        <v>56</v>
+        <v>621</v>
       </c>
       <c r="S124">
         <v>0.85</v>
       </c>
       <c r="T124" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B125" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C125" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F125" t="s">
         <v>24</v>
@@ -7586,33 +7714,33 @@
         <v>2017</v>
       </c>
       <c r="Q125" t="s">
-        <v>628</v>
-      </c>
-      <c r="R125" t="s">
-        <v>56</v>
+        <v>624</v>
       </c>
       <c r="S125">
         <v>0.8</v>
       </c>
       <c r="T125" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B126" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C126" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D126" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F126" t="s">
         <v>24</v>
@@ -7621,36 +7749,36 @@
         <v>2015</v>
       </c>
       <c r="I126" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="Q126" t="s">
-        <v>631</v>
-      </c>
-      <c r="R126" t="s">
-        <v>56</v>
+        <v>627</v>
       </c>
       <c r="S126">
         <v>0.85</v>
       </c>
       <c r="T126" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B127" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C127" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D127" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F127" t="s">
         <v>24</v>
@@ -7659,33 +7787,33 @@
         <v>2016</v>
       </c>
       <c r="Q127" t="s">
-        <v>634</v>
-      </c>
-      <c r="R127" t="s">
-        <v>56</v>
+        <v>630</v>
       </c>
       <c r="S127">
         <v>0.8</v>
       </c>
       <c r="T127" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B128" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D128" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E128" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F128" t="s">
         <v>24</v>
@@ -7694,80 +7822,80 @@
         <v>2008</v>
       </c>
       <c r="H128" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="I128" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="Q128" t="s">
-        <v>639</v>
-      </c>
-      <c r="R128" t="s">
-        <v>46</v>
+        <v>635</v>
       </c>
       <c r="S128">
         <v>0.95</v>
       </c>
       <c r="T128" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>636</v>
+      </c>
+      <c r="B129" t="s">
+        <v>637</v>
+      </c>
+      <c r="C129" t="s">
+        <v>638</v>
+      </c>
+      <c r="D129" t="s">
+        <v>639</v>
+      </c>
+      <c r="F129" t="s">
         <v>640</v>
-      </c>
-      <c r="B129" t="s">
-        <v>641</v>
-      </c>
-      <c r="C129" t="s">
-        <v>642</v>
-      </c>
-      <c r="D129" t="s">
-        <v>643</v>
-      </c>
-      <c r="F129" t="s">
-        <v>644</v>
       </c>
       <c r="G129">
         <v>2013</v>
       </c>
       <c r="H129" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I129" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="P129" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="Q129" t="s">
-        <v>648</v>
-      </c>
-      <c r="R129" t="s">
-        <v>46</v>
+        <v>644</v>
       </c>
       <c r="S129">
         <v>0.85</v>
       </c>
       <c r="T129" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B130" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C130" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D130" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E130" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F130" t="s">
         <v>24</v>
@@ -7776,39 +7904,39 @@
         <v>2017</v>
       </c>
       <c r="H130" t="s">
+        <v>647</v>
+      </c>
+      <c r="I130" t="s">
+        <v>648</v>
+      </c>
+      <c r="L130" t="s">
+        <v>649</v>
+      </c>
+      <c r="M130" t="s">
+        <v>650</v>
+      </c>
+      <c r="Q130" t="s">
         <v>651</v>
-      </c>
-      <c r="I130" t="s">
-        <v>652</v>
-      </c>
-      <c r="L130" t="s">
-        <v>653</v>
-      </c>
-      <c r="M130" t="s">
-        <v>654</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>655</v>
-      </c>
-      <c r="R130" t="s">
-        <v>46</v>
       </c>
       <c r="S130">
         <v>0.98</v>
       </c>
       <c r="T130" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B131" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D131" t="s">
         <v>22</v>
@@ -7823,33 +7951,33 @@
         <v>2004</v>
       </c>
       <c r="Q131" t="s">
-        <v>657</v>
-      </c>
-      <c r="R131" t="s">
-        <v>56</v>
+        <v>653</v>
       </c>
       <c r="S131">
         <v>0.55000000000000004</v>
       </c>
       <c r="T131" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B132" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C132" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D132" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F132" t="s">
         <v>24</v>
@@ -7858,42 +7986,42 @@
         <v>2022</v>
       </c>
       <c r="I132" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="L132" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="M132" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="Q132" t="s">
-        <v>663</v>
-      </c>
-      <c r="R132" t="s">
-        <v>56</v>
+        <v>659</v>
       </c>
       <c r="S132">
         <v>0.9</v>
       </c>
       <c r="T132" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C133" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D133" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F133" t="s">
         <v>24</v>
@@ -7902,39 +8030,39 @@
         <v>2015</v>
       </c>
       <c r="K133" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="P133" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q133" t="s">
-        <v>667</v>
-      </c>
-      <c r="R133" t="s">
-        <v>56</v>
+        <v>663</v>
       </c>
       <c r="S133">
         <v>0.8</v>
       </c>
       <c r="T133" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B134" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C134" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D134" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -7943,36 +8071,36 @@
         <v>2010</v>
       </c>
       <c r="I134" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q134" t="s">
-        <v>670</v>
-      </c>
-      <c r="R134" t="s">
-        <v>56</v>
+        <v>666</v>
       </c>
       <c r="S134">
         <v>0.85</v>
       </c>
       <c r="T134" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B135" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C135" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F135" t="s">
         <v>24</v>
@@ -7981,27 +8109,27 @@
         <v>2008</v>
       </c>
       <c r="I135" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="Q135" t="s">
-        <v>672</v>
-      </c>
-      <c r="R135" t="s">
-        <v>56</v>
+        <v>668</v>
       </c>
       <c r="S135">
         <v>0.85</v>
       </c>
       <c r="T135" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B136" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C136" t="s">
         <v>21</v>
@@ -8019,36 +8147,36 @@
         <v>2003</v>
       </c>
       <c r="H136" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="I136" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P136" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q136" t="s">
-        <v>676</v>
-      </c>
-      <c r="R136" t="s">
-        <v>46</v>
+        <v>672</v>
       </c>
       <c r="S136">
         <v>0.95</v>
       </c>
       <c r="T136" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B137" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D137" t="s">
         <v>22</v>
@@ -8063,36 +8191,36 @@
         <v>2006</v>
       </c>
       <c r="I137" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="Q137" t="s">
-        <v>678</v>
-      </c>
-      <c r="R137" t="s">
-        <v>56</v>
+        <v>674</v>
       </c>
       <c r="S137">
         <v>0.85</v>
       </c>
       <c r="T137" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="U137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B138" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C138" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D138" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F138" t="s">
         <v>24</v>
@@ -8101,45 +8229,45 @@
         <v>2013</v>
       </c>
       <c r="H138" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="I138" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L138" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="M138" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="Q138" t="s">
-        <v>683</v>
-      </c>
-      <c r="R138" t="s">
-        <v>46</v>
+        <v>679</v>
       </c>
       <c r="S138">
         <v>0.98</v>
       </c>
       <c r="T138" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="U138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B139" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C139" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D139" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F139" t="s">
         <v>24</v>
@@ -8148,22 +8276,158 @@
         <v>2011</v>
       </c>
       <c r="H139" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="I139" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="Q139" t="s">
-        <v>687</v>
-      </c>
-      <c r="R139" t="s">
-        <v>46</v>
+        <v>683</v>
       </c>
       <c r="S139">
         <v>0.95</v>
       </c>
       <c r="T139" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="U139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>695</v>
+      </c>
+      <c r="B140" t="s">
+        <v>696</v>
+      </c>
+      <c r="C140" t="s">
+        <v>697</v>
+      </c>
+      <c r="D140" t="s">
+        <v>203</v>
+      </c>
+      <c r="E140" t="s">
+        <v>204</v>
+      </c>
+      <c r="F140" t="s">
+        <v>24</v>
+      </c>
+      <c r="G140">
+        <v>2008</v>
+      </c>
+      <c r="H140" s="2">
+        <v>39670</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140" t="s">
+        <v>699</v>
+      </c>
+      <c r="M140" t="s">
+        <v>704</v>
+      </c>
+      <c r="P140" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>706</v>
+      </c>
+      <c r="R140" t="s">
+        <v>707</v>
+      </c>
+      <c r="S140" t="s">
+        <v>705</v>
+      </c>
+      <c r="T140" t="b">
+        <v>0</v>
+      </c>
+      <c r="U140" t="b">
+        <v>1</v>
+      </c>
+      <c r="V140" t="s">
+        <v>696</v>
+      </c>
+      <c r="W140" t="s">
+        <v>700</v>
+      </c>
+      <c r="X140" t="s">
+        <v>701</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>702</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>703</v>
+      </c>
+      <c r="AB140" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="141" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>708</v>
+      </c>
+      <c r="B141" t="s">
+        <v>709</v>
+      </c>
+      <c r="C141" t="s">
+        <v>710</v>
+      </c>
+      <c r="D141" t="s">
+        <v>22</v>
+      </c>
+      <c r="E141" t="s">
+        <v>23</v>
+      </c>
+      <c r="F141" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141">
+        <v>2002</v>
+      </c>
+      <c r="H141" s="2">
+        <v>37527</v>
+      </c>
+      <c r="J141" t="s">
+        <v>711</v>
+      </c>
+      <c r="M141" t="s">
+        <v>712</v>
+      </c>
+      <c r="P141" t="s">
+        <v>713</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>714</v>
+      </c>
+      <c r="R141" t="s">
+        <v>715</v>
+      </c>
+      <c r="S141" t="s">
+        <v>705</v>
+      </c>
+      <c r="T141" t="b">
+        <v>0</v>
+      </c>
+      <c r="U141" t="b">
+        <v>1</v>
+      </c>
+      <c r="V141" t="s">
+        <v>709</v>
+      </c>
+      <c r="W141" t="s">
+        <v>716</v>
+      </c>
+      <c r="X141" t="s">
+        <v>717</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>718</v>
+      </c>
+      <c r="AB141" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
